--- a/data/raw/客服实测记录.xlsx
+++ b/data/raw/客服实测记录.xlsx
@@ -601,10 +601,6 @@
           <t>实测统计（自动计算，不要手改）</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -646,7 +642,7 @@
       </c>
       <c r="C3" s="6">
         <f>COUNTIF(实测记录!$E$4:$E$33,"答对")+COUNTIF(实测记录!$E$4:$E$33,"答偏")</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="D3" s="7" t="n"/>
       <c r="E3" s="8" t="inlineStr">
@@ -668,7 +664,7 @@
       </c>
       <c r="C4" s="6">
         <f>COUNTIF(实测记录!$E$4:$E$33,"答对")</f>
-        <v>21</v>
+        <v/>
       </c>
       <c r="D4" s="7" t="n"/>
       <c r="E4" s="8" t="inlineStr">
@@ -690,7 +686,7 @@
       </c>
       <c r="C5" s="6">
         <f>COUNTIF(实测记录!$E$4:$E$33,"答偏")</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="D5" s="7" t="n"/>
       <c r="E5" s="8" t="inlineStr">
@@ -712,7 +708,7 @@
       </c>
       <c r="C6" s="10">
         <f>IF(OR(C3="",C3=0),"",C5/C3)</f>
-        <v>0.3</v>
+        <v/>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="8" t="inlineStr">
@@ -734,11 +730,11 @@
       </c>
       <c r="C7" s="6">
         <f>COUNTIF(实测记录!$F$4:$F$33,"语料未覆盖")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D7" s="7">
         <f>IF(OR($C$5="",$C$5=0),"",C7/$C$5)</f>
-        <v>0.1111111111111111</v>
+        <v/>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
@@ -759,11 +755,11 @@
       </c>
       <c r="C8" s="6">
         <f>COUNTIF(实测记录!$F$4:$F$33,"知识库缺失")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D8" s="7">
         <f>IF(OR($C$5="",$C$5=0),"",C8/$C$5)</f>
-        <v>0.1111111111111111</v>
+        <v/>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
@@ -784,11 +780,11 @@
       </c>
       <c r="C9" s="6">
         <f>COUNTIF(实测记录!$F$4:$F$33,"意图识别错")</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="D9" s="7">
         <f>IF(OR($C$5="",$C$5=0),"",C9/$C$5)</f>
-        <v>0.7777777777777778</v>
+        <v/>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
@@ -809,11 +805,11 @@
       </c>
       <c r="C10" s="6">
         <f>COUNTIFS(实测记录!$B$4:$B$33,"退款",实测记录!$E$4:$E$33,"答偏")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="D10" s="7">
         <f>IF(OR($C$5="",$C$5=0),"",C10/$C$5)</f>
-        <v>0.3333333333333333</v>
+        <v/>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
@@ -834,11 +830,11 @@
       </c>
       <c r="C11" s="6">
         <f>COUNTIFS(实测记录!$B$4:$B$33,"改单",实测记录!$E$4:$E$33,"答偏")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D11" s="7">
         <f>IF(OR($C$5="",$C$5=0),"",C11/$C$5)</f>
-        <v>0.1111111111111111</v>
+        <v/>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
@@ -859,11 +855,11 @@
       </c>
       <c r="C12" s="6">
         <f>COUNTIFS(实测记录!$B$4:$B$33,"物流",实测记录!$E$4:$E$33,"答偏")</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="D12" s="7">
         <f>IF(OR($C$5="",$C$5=0),"",C12/$C$5)</f>
-        <v>0.4444444444444444</v>
+        <v/>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -884,11 +880,11 @@
       </c>
       <c r="C13" s="6">
         <f>COUNTIFS(实测记录!$B$4:$B$33,"催件",实测记录!$E$4:$E$33,"答偏")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D13" s="7">
         <f>IF(OR($C$5="",$C$5=0),"",C13/$C$5)</f>
-        <v>0.1111111111111111</v>
+        <v/>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -928,12 +924,6 @@
           <t>AI 客服应答实测记录</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="12" t="n"/>
-      <c r="F1" s="12" t="n"/>
-      <c r="G1" s="12" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -943,7 +933,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>支付宝「我的客服」（蚂蚁智服）</t>
+          <t>某第三方支付平台的在线客服</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -997,7 +987,7 @@
     <row r="4">
       <c r="A4" s="6">
         <f>ROW()-3</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
@@ -1033,7 +1023,7 @@
     <row r="5">
       <c r="A5" s="6">
         <f>ROW()-3</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
@@ -1069,7 +1059,7 @@
     <row r="6">
       <c r="A6" s="6">
         <f>ROW()-3</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
@@ -1105,7 +1095,7 @@
     <row r="7">
       <c r="A7" s="6">
         <f>ROW()-3</f>
-        <v>4</v>
+        <v/>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
@@ -1141,7 +1131,7 @@
     <row r="8">
       <c r="A8" s="6">
         <f>ROW()-3</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
@@ -1177,7 +1167,7 @@
     <row r="9">
       <c r="A9" s="6">
         <f>ROW()-3</f>
-        <v>6</v>
+        <v/>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
@@ -1213,7 +1203,7 @@
     <row r="10">
       <c r="A10" s="6">
         <f>ROW()-3</f>
-        <v>7</v>
+        <v/>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -1249,7 +1239,7 @@
     <row r="11">
       <c r="A11" s="6">
         <f>ROW()-3</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -1285,7 +1275,7 @@
     <row r="12">
       <c r="A12" s="6">
         <f>ROW()-3</f>
-        <v>9</v>
+        <v/>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
@@ -1321,7 +1311,7 @@
     <row r="13">
       <c r="A13" s="6">
         <f>ROW()-3</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -1357,7 +1347,7 @@
     <row r="14">
       <c r="A14" s="6">
         <f>ROW()-3</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
@@ -1393,7 +1383,7 @@
     <row r="15">
       <c r="A15" s="6">
         <f>ROW()-3</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
@@ -1429,7 +1419,7 @@
     <row r="16">
       <c r="A16" s="6">
         <f>ROW()-3</f>
-        <v>13</v>
+        <v/>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
@@ -1465,7 +1455,7 @@
     <row r="17">
       <c r="A17" s="6">
         <f>ROW()-3</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -1501,7 +1491,7 @@
     <row r="18">
       <c r="A18" s="6">
         <f>ROW()-3</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
@@ -1537,7 +1527,7 @@
     <row r="19">
       <c r="A19" s="6">
         <f>ROW()-3</f>
-        <v>16</v>
+        <v/>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
@@ -1573,7 +1563,7 @@
     <row r="20">
       <c r="A20" s="6">
         <f>ROW()-3</f>
-        <v>17</v>
+        <v/>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
@@ -1609,7 +1599,7 @@
     <row r="21">
       <c r="A21" s="6">
         <f>ROW()-3</f>
-        <v>18</v>
+        <v/>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
@@ -1645,7 +1635,7 @@
     <row r="22">
       <c r="A22" s="6">
         <f>ROW()-3</f>
-        <v>19</v>
+        <v/>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
@@ -1681,7 +1671,7 @@
     <row r="23">
       <c r="A23" s="6">
         <f>ROW()-3</f>
-        <v>20</v>
+        <v/>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
@@ -1717,7 +1707,7 @@
     <row r="24">
       <c r="A24" s="6">
         <f>ROW()-3</f>
-        <v>21</v>
+        <v/>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
@@ -1753,7 +1743,7 @@
     <row r="25">
       <c r="A25" s="6">
         <f>ROW()-3</f>
-        <v>22</v>
+        <v/>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
@@ -1789,7 +1779,7 @@
     <row r="26">
       <c r="A26" s="6">
         <f>ROW()-3</f>
-        <v>23</v>
+        <v/>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
@@ -1825,7 +1815,7 @@
     <row r="27">
       <c r="A27" s="6">
         <f>ROW()-3</f>
-        <v>24</v>
+        <v/>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
@@ -1861,7 +1851,7 @@
     <row r="28">
       <c r="A28" s="6">
         <f>ROW()-3</f>
-        <v>25</v>
+        <v/>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
@@ -1897,7 +1887,7 @@
     <row r="29">
       <c r="A29" s="6">
         <f>ROW()-3</f>
-        <v>26</v>
+        <v/>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
@@ -1933,7 +1923,7 @@
     <row r="30">
       <c r="A30" s="6">
         <f>ROW()-3</f>
-        <v>27</v>
+        <v/>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
@@ -1969,7 +1959,7 @@
     <row r="31">
       <c r="A31" s="6">
         <f>ROW()-3</f>
-        <v>28</v>
+        <v/>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
@@ -2005,7 +1995,7 @@
     <row r="32">
       <c r="A32" s="6">
         <f>ROW()-3</f>
-        <v>29</v>
+        <v/>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
@@ -2041,7 +2031,7 @@
     <row r="33">
       <c r="A33" s="6">
         <f>ROW()-3</f>
-        <v>30</v>
+        <v/>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
@@ -2055,7 +2045,7 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>明确24小时内完成审核，通过【服务提醒】反馈结果；可在【支付宝举报中心】查记录与结果；不认可可补充凭证申请重审。</t>
+          <t>明确24小时内完成审核，通过【服务提醒】反馈结果；可在【该平台举报中心】查记录与结果；不认可可补充凭证申请重审。</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -2126,7 +2116,6 @@
           <t>AI 客服应答实测 · 操作说明</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
